--- a/Planning_optimise.xlsx
+++ b/Planning_optimise.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Omar Bouzid</t>
+          <t>Youssef El Amrani</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -555,12 +555,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Youssef El Amrani</t>
+          <t>Omar Bouzid</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Omar Bouzid</t>
+          <t>Khadija Bencheikh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Khadija Bencheikh</t>
+          <t>Youssef El Amrani</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Youssef El Amrani</t>
+          <t>Khadija Bencheikh</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -690,7 +690,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Omar Bouzid</t>
+          <t>Khadija Bencheikh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Khadija Bencheikh</t>
+          <t>Youssef El Amrani</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -744,7 +744,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Lundi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pédiatrie</t>
+          <t>Urgences</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Khadija Bencheikh</t>
+          <t>Omar Bouzid</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Lundi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pédiatrie</t>
+          <t>Urgences</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Youssef El Amrani</t>
+          <t>Salma El Fassi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lundi</t>
+          <t>Mardi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -825,7 +825,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lundi</t>
+          <t>Mardi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -852,12 +852,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -879,12 +879,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Salma El Fassi</t>
+          <t>Omar Bouzid</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hicham Touimi</t>
+          <t>Fatima Zahra El Idrissi</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fatima Zahra El Idrissi</t>
+          <t>Hicham Touimi</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Fatima Zahra El Idrissi</t>
+          <t>Hicham Touimi</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hicham Touimi</t>
+          <t>Fatima Zahra El Idrissi</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1662,7 +1662,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Vendredi</t>
+          <t>Mardi</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mardi</t>
+          <t>Jeudi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Urgences</t>
+          <t>Pédiatrie</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1716,7 +1716,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mercredi</t>
+          <t>Vendredi</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Urgences</t>
+          <t>Pédiatrie</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jeudi</t>
+          <t>Mercredi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2419570</v>
+        <v>2419675.5555553</v>
       </c>
     </row>
   </sheetData>
